--- a/results/latest.xlsx
+++ b/results/latest.xlsx
@@ -62,7 +62,7 @@
     <t>Retest Confirmed</t>
   </si>
   <si>
-    <t>Strict signals — ALL 5 conditions met.  Run: 2026-10-12 10:49</t>
+    <t>Strict signals — ALL 5 conditions met.  Run: 2026-10-13 10:35</t>
   </si>
   <si>
     <t>No stocks passed all 5 conditions today. See the Watchlist sheet.</t>
@@ -1895,7 +1895,7 @@
     <t>Stock Breakout Scanner</t>
   </si>
   <si>
-    <t>Run time: 2026-10-12 10:49:22  |  Data as of EOD: 2026-10-09</t>
+    <t>Run time: 2026-10-13 10:35:40  |  Data as of EOD: 2026-10-09</t>
   </si>
   <si>
     <t>Note: 'Current Price' = last completed daily close (EOD), not a live intraday price. Ties exactly to NSE Bhavcopy.</t>
